--- a/data/trans_camb/IP07_R2-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP07_R2-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-1,23</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-2,64</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1,92</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-2,36</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-1,24</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>7,76</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-1,23</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-2,64</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,04</t>
+          <t>-1,06</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,75</t>
+          <t>0,61</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,13; 1,9</t>
+          <t>-7,06; 4,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,03; 4,89</t>
+          <t>-8,43; 2,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 37,04</t>
+          <t>-4,62; 11,07</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,31; 4,21</t>
+          <t>-7,89; 1,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-7,86; 2,62</t>
+          <t>-6,23; 4,84</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-3,97; 10,64</t>
+          <t>-6,27; 6,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 1,52</t>
+          <t>-4,88; 1,79</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-5,41; 1,91</t>
+          <t>-5,45; 2,03</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 19,0</t>
+          <t>-3,82; 5,6</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-22,12%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-47,23%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>34,47%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>-47,63%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>-25,08%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>156,61%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-22,12%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-47,23%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>-21,46%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>11,64%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-89,98; 116,21</t>
+          <t>-86,71; 162,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 266,28</t>
+          <t>-100,0; 115,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-85,89; 2082,43</t>
+          <t>-64,29; 429,53</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-77,03; 194,48</t>
+          <t>-89,0; 96,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 141,81</t>
+          <t>-100,0; 227,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-60,35; 414,35</t>
+          <t>-88,22; 478,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-74,14; 56,55</t>
+          <t>-70,76; 59,55</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-80,44; 90,0</t>
+          <t>-78,08; 71,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-34,01; 505,7</t>
+          <t>-57,32; 175,33</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-0,77</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-1,03</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-1,77</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,24</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,59</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,96</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,77</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-1,03</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-1,74</t>
+          <t>1,12</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-0,47</t>
+          <t>-0,41</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 2,94</t>
+          <t>-2,56; 0,99</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,76; 2,06</t>
+          <t>-2,65; 0,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,57</t>
+          <t>-3,28; 0,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,49; 0,93</t>
+          <t>-0,36; 2,93</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-2,89; 0,7</t>
+          <t>-0,84; 2,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,49; -0,27</t>
+          <t>-0,52; 2,92</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,34</t>
+          <t>-1,12; 1,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-1,36; 0,8</t>
+          <t>-1,4; 0,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 0,67</t>
+          <t>-1,5; 0,83</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-22,81%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-30,56%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-52,49%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>79,57%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>37,94%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>61,44%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-22,81%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-30,56%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-51,61%</t>
+          <t>71,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-18,77%</t>
+          <t>-16,21%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-24,22; 318,07</t>
+          <t>-57,41; 43,86</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-36,32; 230,46</t>
+          <t>-62,68; 25,07</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-28,85; 276,96</t>
+          <t>-77,61; 5,21</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-57,99; 40,83</t>
+          <t>-21,26; 312,7</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-65,98; 32,29</t>
+          <t>-44,48; 228,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-77,77; -0,88</t>
+          <t>-30,23; 328,59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-32,96; 69,33</t>
+          <t>-34,56; 70,28</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-45,01; 41,94</t>
+          <t>-44,51; 48,83</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-52,3; 34,47</t>
+          <t>-49,76; 47,26</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>-1,62</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-1,79</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>0,21</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,58</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,26</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,35</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-1,62</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-1,79</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,1</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,93</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 2,76</t>
+          <t>-4,06; 1,03</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,38</t>
+          <t>-4,78; 0,3</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 4,44</t>
+          <t>-2,88; 3,84</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 0,72</t>
+          <t>-0,48; 2,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 0,26</t>
+          <t>-0,79; 1,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 3,55</t>
+          <t>-0,18; 4,69</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 1,07</t>
+          <t>-1,83; 1,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-2,13; 0,58</t>
+          <t>-2,32; 0,51</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 2,91</t>
+          <t>-0,84; 3,18</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>-55,42%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-61,42%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>7,15%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>158,42%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>72,3%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>371,3%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>-55,42%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>-61,42%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>397,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>54,12%</t>
+          <t>58,92%</t>
         </is>
       </c>
     </row>
@@ -1220,42 +1220,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
+          <t>-100,0; 102,2</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>-74,06; 302,23</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 105,23</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 64,09</t>
-        </is>
-      </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-72,1; 294,84</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-83,23; 184,53</t>
+          <t>-81,99; 178,02</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-86,11; 94,86</t>
+          <t>-92,07; 58,01</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-49,37; 353,55</t>
+          <t>-48,27; 358,35</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-1,03</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-1,45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-1,09</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>0,63</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>0,2</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>1,47</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-1,03</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-1,45</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-1,08</t>
+          <t>0,86</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,14</t>
+          <t>-0,15</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-0,58; 1,96</t>
+          <t>-2,46; 0,35</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 1,4</t>
+          <t>-2,98; -0,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,04; 4,9</t>
+          <t>-2,68; 0,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,47; 0,38</t>
+          <t>-0,6; 1,83</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,93; -0,11</t>
+          <t>-0,97; 1,34</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 0,38</t>
+          <t>-0,43; 2,45</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 0,75</t>
+          <t>-1,22; 0,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 0,25</t>
+          <t>-1,48; 0,32</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,63</t>
+          <t>-1,04; 0,88</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-29,27%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-40,89%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-30,83%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>37,05%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>11,97%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>86,02%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>-29,27%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>-40,89%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-30,67%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>-5,48%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-28,13; 159,34</t>
+          <t>-57,2; 13,5</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-41,7; 122,02</t>
+          <t>-68,09; -3,07</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-6,46; 340,43</t>
+          <t>-61,43; 15,74</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-56,71; 16,01</t>
+          <t>-28,29; 162,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-66,31; 0,62</t>
+          <t>-41,59; 117,53</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-62,45; 14,97</t>
+          <t>-22,14; 215,87</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-37,84; 33,54</t>
+          <t>-38,74; 34,6</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-49,97; 10,68</t>
+          <t>-48,18; 15,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-32,33; 71,23</t>
+          <t>-33,94; 42,92</t>
         </is>
       </c>
     </row>
